--- a/data_extactor/batch/201_250.xlsx
+++ b/data_extactor/batch/201_250.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4A5698-835B-4B5A-9178-732EDBE6CA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43233E7D-DED9-4FA5-987A-4C2D3D1C0E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="541">
   <si>
     <t>17-3027.00</t>
   </si>
@@ -1540,6 +1540,114 @@
   </si>
   <si>
     <t>Advise government agencies, private organizations, and communities regarding proposed programs, plans, and policies and their potential impacts on cultural institutions, organizations, and communities. | Apply traditional ecological knowledge and assessments of culturally distinctive land and resource management institutions to assist in the resolution of conflicts over habitat protection and resource enhancement. | Assess archeological sites for resource management, development, or conservation purposes and recommend methods for site protection. | Clean, restore, and preserve artifacts. | Collaborate with economic development planners to decide on the implementation of proposed development policies, plans, and programs based on culturally institutionalized barriers and facilitating circumstances. | Collect artifacts made of stone, bone, metal, and other materials, placing them in bags and marking them to show where they were found. | Collect information and make judgments through observation, interviews, and review of documents. | Compare findings from one site with archeological data from other sites to find similarities or differences. | Conduct participatory action research in communities and organizations to assess how work is done and to design work systems, technologies, and environments. | Consult site reports, existing artifacts, and topographic maps to identify archeological sites. | Create data records for use in describing and analyzing social patterns and processes, using photography, videography, and audio recordings. | Describe artifacts' physical properties or attributes, such as the materials from which artifacts are made and their size, shape, function, and decoration. | Develop and test theories concerning the origin and development of past cultures. | Develop intervention procedures, using techniques such as individual and focus group interviews, consultations, and participant observation of social interaction. | Enhance the cultural sensitivity of elementary and secondary curricula and classroom interactions in collaboration with educators and teachers. | Formulate general rules that describe and predict the development and behavior of cultures and social institutions. | Gather and analyze artifacts and skeletal remains to increase knowledge of ancient cultures. | Identify culturally specific beliefs and practices affecting health status and access to services for distinct populations and communities, in collaboration with medical and public health officials. | Lead field training sites and train field staff, students, and volunteers in excavation methods. | Organize public exhibits and displays to promote public awareness of diverse and distinctive cultural traditions. | Participate in forensic activities, such as tooth and bone structure identification, in conjunction with police departments and pathologists. | Plan and direct research to characterize and compare the economic, demographic, health care, social, political, linguistic, and religious institutions of distinct cultural groups, communities, and organizations. | Record the exact locations and conditions of artifacts uncovered in diggings or surveys, using drawings and photographs as necessary. | Research, survey, or assess sites of past societies and cultures in search of answers to specific research questions. | Study archival collections of primary historical sources to help explain the origins and development of cultural patterns. | Study objects and structures recovered by excavation to identify, date, and authenticate them and to interpret their significance. | Teach or mentor undergraduate and graduate students in anthropology or archeology. | Train others in the application of ethnographic research methods to solve problems in organizational effectiveness, communications, technology development, policy making, and program planning. | Write about and present research findings for a variety of specialized and general audiences. | Write grant proposals to obtain funding for research.</t>
+  </si>
+  <si>
+    <t>Calibration Specialist | Calibration Technician | Calibration Technologist | Instrument Calibration Technician | Metrology Technician | Metrologist | Standards Technician | Test and Calibration Technician | Gauge Technician | Measurement Technician</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Mathematics | Engineering and Technology | Computers and Electronics | Physics | Mechanical | English Language | Production and Processing | Design</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Importance of Being Exact or Accurate | Consequence of Error | Indoors, Not Environmentally Controlled | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Importance of Repeating Same Tasks | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Health and Safety of Other Workers | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Engineering Technician | Engineering Technologist | Field Engineering Technician | Instrumentation Technician | Laboratory Technician | Process Technician | Product Test Technician | Quality Technician | Research Technician | Test Technician</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | ANSYS simulation software | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | Three-dimensional 3D computer aided design CAD software | Two-dimensional 2D computer aided design CAD software | Email software | Microsoft PowerPoint | Statistical process control SPC software | Minitab</t>
+  </si>
+  <si>
+    <t>Engineering and Technology | Mathematics | Computers and Electronics | Physics | Mechanical | English Language | Design | Production and Processing</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Indoors, Not Environmentally Controlled | Importance of Being Exact or Accurate | Consequence of Error | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Health and Safety of Other Workers | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Non-Destructive Testing Specialists | Photonics Technicians | Civil Engineering Technologists and Technicians | Electrical and Electronic Engineering Technologists and Technicians | Mechanical Engineering Technologists and Technicians | Industrial Engineering Technologists and Technicians | Environmental Engineering Technologists and Technicians | Electro-Mechanical and Mechatronics Technologists and Technicians | Aerospace Engineering and Operations Technologists and Technicians | Calibration Technologists and Technicians | Robotics Technicians | Nanotechnology Engineering Technologists and Technicians | Automotive Engineering Technicians | Surveying and Mapping Technicians | Architectural and Civil Drafters | Mechanical Drafters | Electrical and Electronics Drafters | Industrial Engineers | Mechanical Engineers | Quality Control Systems Managers</t>
+  </si>
+  <si>
+    <t>Apply engineering theory and technical skills in specialties not classified separately. | Set up, calibrate, and operate test equipment and instrumentation. | Conduct tests and experiments and record measurements and observations. | Analyze test data and prepare reports summarizing results and deviations. | Assist engineers in developing, building, and modifying prototypes and test fixtures. | Inspect components and assemblies to verify conformance to specifications. | Troubleshoot equipment malfunctions and perform corrective maintenance. | Maintain calibration records, test logs, and quality documentation. | Prepare sketches, diagrams, and technical documentation supporting engineering work. | Install, configure, and commission equipment and control systems. | Recommend improvements to test methods, procedures, and equipment. | Ensure compliance with safety procedures and quality standards during testing. | Order materials, components, and supplies required for technical work. | Train operators and junior technicians on equipment and procedures.</t>
+  </si>
+  <si>
+    <t>Biological Scientist | Cell Biologist | Developmental Biologist | Ecologist | Entomologist | Immunologist | Marine Biologist | Physiologist | Toxicologist | Virologist</t>
+  </si>
+  <si>
+    <t>Laboratory information management system LIMS | Microsoft Excel | Microsoft Word | IBM SPSS Statistics | SAS | R | Python | Database software | Email software | Microsoft PowerPoint | Minitab | Web browser software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Mathematics | Active Learning | Writing | Speaking | Active Listening | Science | Monitoring</t>
+  </si>
+  <si>
+    <t>Biology | Chemistry | Mathematics | English Language | Computers and Electronics | Education and Training | Physics | Administration and Management | Medicine and Dentistry</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Consequence of Error | Importance of Repeating Same Tasks</t>
+  </si>
+  <si>
+    <t>Zoologists and Wildlife Biologists | Microbiologists | Biochemists and Biophysicists | Molecular and Cellular Biologists | Geneticists | Biologists | Bioinformatics Scientists | Animal Scientists | Soil and Plant Scientists | Food Scientists and Technologists | Medical Scientists, Except Epidemiologists | Epidemiologists | Conservation Scientists | Foresters | Environmental Scientists and Specialists, Including Health | Biological Technicians | Biological Science Teachers, Postsecondary | Natural Sciences Managers | Range Managers | Park Naturalists</t>
+  </si>
+  <si>
+    <t>Conduct research in biological specialties not classified separately. | Design and carry out laboratory and field experiments to test scientific hypotheses. | Collect, prepare, and analyze biological samples using established protocols. | Operate and maintain laboratory instruments, cultures, and specimen collections. | Analyze experimental data using statistical and computational methods. | Prepare technical reports, research papers, and grant proposals. | Present research findings at scientific conferences and to sponsoring organizations. | Review scientific literature to remain current with developments in the field. | Supervise and train laboratory technicians, students, and research assistants. | Ensure compliance with biosafety, animal care, and research ethics requirements. | Develop and validate new analytical methods and experimental procedures. | Maintain detailed laboratory notebooks and research documentation. | Collaborate with other scientists and institutions on joint research projects. | Advise on the application of biological findings to industry, medicine, or conservation.</t>
+  </si>
+  <si>
+    <t>Biomedical Scientist | Biosafety Scientist | Biotechnologist | Life Scientist | Life Sciences Researcher | Marine Scientist | Nutrition Scientist | Pharmacologist | Research Scientist | Wildlife Scientist</t>
+  </si>
+  <si>
+    <t>Biology | Chemistry | Mathematics | English Language | Medicine and Dentistry | Computers and Electronics | Education and Training | Administration and Management | Physics</t>
+  </si>
+  <si>
+    <t>Biologists | Microbiologists | Biochemists and Biophysicists | Molecular and Cellular Biologists | Geneticists | Bioinformatics Scientists | Medical Scientists, Except Epidemiologists | Epidemiologists | Zoologists and Wildlife Biologists | Animal Scientists | Soil and Plant Scientists | Food Scientists and Technologists | Conservation Scientists | Foresters | Environmental Scientists and Specialists, Including Health | Biological Technicians | Natural Sciences Managers | Biological Science Teachers, Postsecondary | Health Specialties Teachers, Postsecondary | Clinical Research Coordinators</t>
+  </si>
+  <si>
+    <t>Conduct research in life science specialties not classified separately. | Plan and execute laboratory, clinical, or field studies to investigate biological questions. | Develop experimental protocols and select appropriate analytical techniques. | Collect and process biological specimens and record observations systematically. | Interpret research results using statistical analysis and modeling software. | Write scientific manuscripts, technical reports, and regulatory submissions. | Prepare and administer research grants, budgets, and project schedules. | Supervise laboratory personnel and coordinate multi-investigator studies. | Ensure adherence to safety, ethical, and regulatory standards governing research. | Calibrate, operate, and troubleshoot specialized scientific instruments. | Evaluate emerging techniques and technologies for research application. | Present findings to scientific, regulatory, and commercial audiences. | Maintain research records, sample inventories, and data archives. | Advise organizations on the scientific basis of products, policies, or practices.</t>
+  </si>
+  <si>
+    <t>Environmental Chemist | Geophysicist | Metallurgist | Nuclear Scientist | Oceanographer | Optical Scientist | Physical Scientist | Planetary Scientist | Research Physicist | Spectroscopist</t>
+  </si>
+  <si>
+    <t>Laboratory information management system LIMS | Microsoft Excel | Microsoft Word | IBM SPSS Statistics | SAS | R | Python | Database software | Email software | Microsoft PowerPoint | Minitab | Web browser software | The MathWorks MATLAB</t>
+  </si>
+  <si>
+    <t>Physics | Chemistry | Mathematics | English Language | Computers and Electronics | Engineering and Technology | Education and Training | Geography | Administration and Management</t>
+  </si>
+  <si>
+    <t>Chemists | Materials Scientists | Physicists | Astronomers | Atmospheric and Space Scientists | Geoscientists, Except Hydrologists and Geographers | Hydrologists | Environmental Scientists and Specialists, Including Health | Remote Sensing Scientists and Technologists | Industrial Ecologists | Environmental Restoration Planners | Climate Change Policy Analysts | Chemical Technicians | Nuclear Technicians | Geological Technicians, Except Hydrologic Technicians | Chemistry Teachers, Postsecondary | Physics Teachers, Postsecondary | Natural Sciences Managers | Materials Engineers | Nuclear Engineers</t>
+  </si>
+  <si>
+    <t>Conduct research in physical science specialties not classified separately. | Design and perform experiments to investigate physical and chemical phenomena. | Operate specialized instrumentation to measure physical properties and processes. | Develop mathematical and computational models of physical systems. | Analyze experimental and observational data and quantify measurement uncertainty. | Prepare research reports, technical papers, and proposals for funding. | Interpret findings and advise on their industrial or environmental applications. | Calibrate and maintain scientific equipment and verify instrument performance. | Collect field samples and environmental measurements under varied conditions. | Review scientific literature and evaluate new measurement techniques. | Supervise technicians and coordinate laboratory or field operations. | Ensure compliance with safety procedures for hazardous materials and radiation. | Present technical findings to scientific, regulatory, and management audiences. | Maintain detailed records of methods, calibrations, and results.</t>
+  </si>
+  <si>
+    <t>Consumer Psychologist | Developmental Psychologist | Educational Psychologist | Experimental Psychologist | Forensic Psychologist | Health Psychologist | Psychologist | Research Psychologist | Social Psychologist | Sport Psychologist</t>
+  </si>
+  <si>
+    <t>Microsoft Excel | Structured query language SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | Database software | Microsoft Word | Email software | Microsoft PowerPoint | Scheduling software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Psychology | English Language | Therapy and Counseling | Sociology and Anthropology | Education and Training | Mathematics | Customer and Personal Service | Computers and Electronics | Administration and Management</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Conflict Situations | Public Speaking</t>
+  </si>
+  <si>
+    <t>Clinical and Counseling Psychologists | School Psychologists | Industrial-Organizational Psychologists | Neuropsychologists | Clinical Neuropsychologists | Marriage and Family Therapists | Mental Health Counselors | Substance Abuse and Behavioral Disorder Counselors | Rehabilitation Counselors | Educational, Guidance, and Career Counselors and Advisors | Sociologists | Survey Researchers | Social Science Research Assistants | Psychology Teachers, Postsecondary | Healthcare Social Workers | Mental Health and Substance Abuse Social Workers | Medical Scientists, Except Epidemiologists | Anthropologists and Archeologists | Human Resources Specialists | Health Education Specialists</t>
+  </si>
+  <si>
+    <t>Apply psychological principles in specialties not classified separately. | Design and conduct research studies on behavior, cognition, and mental processes. | Administer, score, and interpret psychological tests and assessment instruments. | Analyze research data using statistical software and report findings. | Consult with organizations on human behavior, performance, and program design. | Prepare evaluation reports, case summaries, and expert opinions. | Develop and evaluate interventions, training programs, and behavioral protocols. | Interview clients, subjects, and collateral sources to gather relevant information. | Maintain confidential records in accordance with professional and legal standards. | Publish research findings and present at professional conferences. | Supervise graduate students, interns, and research assistants. | Adhere to professional ethics codes and licensing requirements. | Collaborate with physicians, educators, and other professionals on client cases. | Review literature and maintain competence through continuing education.</t>
   </si>
 </sst>
 </file>
@@ -1937,8 +2045,23 @@
       <c r="B3" t="s">
         <v>23</v>
       </c>
+      <c r="C3" t="s">
+        <v>505</v>
+      </c>
       <c r="D3" t="s">
         <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>506</v>
+      </c>
+      <c r="F3" t="s">
+        <v>507</v>
+      </c>
+      <c r="G3" t="s">
+        <v>508</v>
+      </c>
+      <c r="H3" t="s">
+        <v>509</v>
       </c>
       <c r="I3" t="s">
         <v>25</v>
@@ -1957,8 +2080,32 @@
       <c r="B4" t="s">
         <v>29</v>
       </c>
+      <c r="C4" t="s">
+        <v>510</v>
+      </c>
+      <c r="D4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E4" t="s">
+        <v>506</v>
+      </c>
+      <c r="F4" t="s">
+        <v>512</v>
+      </c>
+      <c r="G4" t="s">
+        <v>508</v>
+      </c>
+      <c r="H4" t="s">
+        <v>513</v>
+      </c>
+      <c r="I4" t="s">
+        <v>514</v>
+      </c>
       <c r="J4" t="s">
         <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2283,8 +2430,32 @@
       <c r="B14" t="s">
         <v>131</v>
       </c>
+      <c r="C14" t="s">
+        <v>516</v>
+      </c>
+      <c r="D14" t="s">
+        <v>517</v>
+      </c>
+      <c r="E14" t="s">
+        <v>518</v>
+      </c>
+      <c r="F14" t="s">
+        <v>519</v>
+      </c>
+      <c r="G14" t="s">
+        <v>520</v>
+      </c>
+      <c r="H14" t="s">
+        <v>521</v>
+      </c>
+      <c r="I14" t="s">
+        <v>522</v>
+      </c>
       <c r="J14" t="s">
         <v>132</v>
+      </c>
+      <c r="K14" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -2644,8 +2815,32 @@
       <c r="B25" t="s">
         <v>244</v>
       </c>
+      <c r="C25" t="s">
+        <v>524</v>
+      </c>
+      <c r="D25" t="s">
+        <v>517</v>
+      </c>
+      <c r="E25" t="s">
+        <v>518</v>
+      </c>
+      <c r="F25" t="s">
+        <v>525</v>
+      </c>
+      <c r="G25" t="s">
+        <v>520</v>
+      </c>
+      <c r="H25" t="s">
+        <v>521</v>
+      </c>
+      <c r="I25" t="s">
+        <v>526</v>
+      </c>
       <c r="J25" t="s">
         <v>245</v>
+      </c>
+      <c r="K25" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -3040,8 +3235,32 @@
       <c r="B37" t="s">
         <v>368</v>
       </c>
+      <c r="C37" t="s">
+        <v>528</v>
+      </c>
+      <c r="D37" t="s">
+        <v>529</v>
+      </c>
+      <c r="E37" t="s">
+        <v>518</v>
+      </c>
+      <c r="F37" t="s">
+        <v>530</v>
+      </c>
+      <c r="G37" t="s">
+        <v>520</v>
+      </c>
+      <c r="H37" t="s">
+        <v>521</v>
+      </c>
+      <c r="I37" t="s">
+        <v>531</v>
+      </c>
       <c r="J37" t="s">
         <v>369</v>
+      </c>
+      <c r="K37" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
@@ -3296,8 +3515,32 @@
       <c r="B45" t="s">
         <v>448</v>
       </c>
+      <c r="C45" t="s">
+        <v>533</v>
+      </c>
+      <c r="D45" t="s">
+        <v>534</v>
+      </c>
+      <c r="E45" t="s">
+        <v>535</v>
+      </c>
+      <c r="F45" t="s">
+        <v>536</v>
+      </c>
+      <c r="G45" t="s">
+        <v>537</v>
+      </c>
+      <c r="H45" t="s">
+        <v>538</v>
+      </c>
+      <c r="I45" t="s">
+        <v>539</v>
+      </c>
       <c r="J45" t="s">
         <v>449</v>
+      </c>
+      <c r="K45" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
